--- a/Data/JTS_Approval.xlsx
+++ b/Data/JTS_Approval.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF37A0A2-D946-4983-8B78-987B272A9FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="26">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -37,43 +38,104 @@
     <t>Primary</t>
   </si>
   <si>
-    <t>Returns (Primary) - WFM Primary Job Transfer Sets</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Secondary</t>
   </si>
   <si>
     <t>Additional Activities (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
-    <t>Operations (Secondary) - WFM Secondary Job Transfer Sets</t>
+    <t>Zone and Maintenance (Primary) - WFM Primary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Fitting Rooms (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Replenishment (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Returns (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>SCO Host (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Tills (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10275715</t>
+  </si>
+  <si>
+    <t>Replenishment (Primary) - WFM Primary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Zone and Maintenance (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10282363</t>
+  </si>
+  <si>
+    <t>Visual Merchandising (Primary) - WFM Primary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10282561</t>
+  </si>
+  <si>
+    <t>Tills (Primary) - WFM Primary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10282676</t>
+  </si>
+  <si>
+    <t>10282979</t>
+  </si>
+  <si>
+    <t>10283047</t>
+  </si>
+  <si>
+    <t>10283288</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -88,7 +150,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -119,11 +188,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -403,14 +483,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
     <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" customWidth="1"/>
+    <col min="4" max="4" width="65" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -433,87 +513,608 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>10205857</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>10282765</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/JTS_Approval.xlsx
+++ b/Data/JTS_Approval.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D2F1F1-D783-4C88-BC95-9FD10C45D6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="21">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -32,108 +31,100 @@
     <t>TestStatus</t>
   </si>
   <si>
-    <t>10283342</t>
-  </si>
-  <si>
-    <t>10196188</t>
+    <t>10270575</t>
   </si>
   <si>
     <t>Secondary</t>
   </si>
   <si>
+    <t>Fitting Rooms (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Returns (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>SCO Host (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
     <t>Tills (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
-    <t>10493793</t>
-  </si>
-  <si>
-    <t>Fitting Rooms (Secondary) - WFM Secondary Job Transfer Sets</t>
-  </si>
-  <si>
-    <t>10513208</t>
-  </si>
-  <si>
-    <t>10513254</t>
+    <t>Additional Activities (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
     <t>Zone and Maintenance (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
-    <t>10545423</t>
+    <t>Primary</t>
   </si>
   <si>
-    <t>SCO Host (Secondary) - WFM Secondary Job Transfer Sets</t>
+    <t>Zone and Maintenance (Primary) - WFM Primary Job Transfer Sets</t>
   </si>
   <si>
-    <t>10545684</t>
+    <t>Replenishment (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
-    <t>10574315</t>
+    <t>Fitting Rooms (Primary) - WFM Primary Job Transfer Sets</t>
   </si>
   <si>
-    <t>Additional Activities (Secondary) - WFM Secondary Job Transfer Sets</t>
+    <t>Replenishment (Primary) - WFM Primary Job Transfer Sets</t>
   </si>
   <si>
-    <t>10580393</t>
+    <t>Cash Office (Primary) - WFM Primary Job Transfer Sets</t>
   </si>
   <si>
-    <t>10596680</t>
-  </si>
-  <si>
-    <t>10622999</t>
-  </si>
-  <si>
-    <t>Returns (Secondary) - WFM Secondary Job Transfer Sets</t>
+    <t>Tills (Primary) - WFM Primary Job Transfer Sets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color indexed="8"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <color indexed="8"/>
+      <family val="2"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="10"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,12 +145,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -188,39 +185,31 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -229,14 +218,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF00B050"/>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -515,18 +504,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E113"/>
+  <sheetFormatPr defaultRowHeight="14.45" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" customWidth="1"/>
-    <col min="4" max="4" width="57.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.109375" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,322 +532,1587 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
+    <row r="2" ht="14.45" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>10499785</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="3" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>10499785</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="4" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>10499785</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="5" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>10499785</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>10499785</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>10499785</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+    </row>
+    <row r="10" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+    </row>
+    <row r="14" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>10499961</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="18" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <v>10499962</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="24" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="25" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>10499969</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="29" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>10499975</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="3" t="s">
+    </row>
+    <row r="38" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="39" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>10499979</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>10500058</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="D43" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="47" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>10500065</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="57" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>10500792</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="59" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="3" t="s">
+    </row>
+    <row r="60" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="4" t="s">
+    </row>
+    <row r="61" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
+    <row r="62" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>10514556</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="66" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="67" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>10562493</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="73" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="4" t="s">
+    </row>
+    <row r="75" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="76" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>10578693</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="82" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>10585378</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="87" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="4" t="s">
+    </row>
+    <row r="88" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" s="6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="89" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>10585567</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>10590397</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="101" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="3" t="s">
+    </row>
+    <row r="102" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="103" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="105" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>10590411</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="D107" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="4"/>
-    </row>
-    <row r="15" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="4"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="4"/>
-    </row>
-    <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="5"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="4"/>
-    </row>
-    <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="5"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="4"/>
-    </row>
-    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="4"/>
-    </row>
-    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="5"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="4"/>
-    </row>
-    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="4"/>
-    </row>
-    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="4"/>
-    </row>
-    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="4"/>
-    </row>
-    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="4"/>
-    </row>
-    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="4"/>
-    </row>
-    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="4"/>
-    </row>
-    <row r="27" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="4"/>
-    </row>
-    <row r="28" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="4"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="4"/>
+    <row r="111" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" ht="14.45" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>10593883</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="E1 E22:E1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Failed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"Passed"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/JTS_Approval.xlsx
+++ b/Data/JTS_Approval.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D2F1F1-D783-4C88-BC95-9FD10C45D6C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="24">
   <si>
     <t>EmployeeID</t>
   </si>
@@ -31,49 +32,108 @@
     <t>TestStatus</t>
   </si>
   <si>
-    <t>10052303</t>
-  </si>
-  <si>
-    <t>Primary</t>
-  </si>
-  <si>
-    <t>Returns (Primary) - WFM Primary Job Transfer Sets</t>
+    <t>10283342</t>
+  </si>
+  <si>
+    <t>10196188</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>Tills (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>Secondary</t>
+    <t>10493793</t>
+  </si>
+  <si>
+    <t>Fitting Rooms (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10513208</t>
+  </si>
+  <si>
+    <t>10513254</t>
+  </si>
+  <si>
+    <t>Zone and Maintenance (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10545423</t>
+  </si>
+  <si>
+    <t>SCO Host (Secondary) - WFM Secondary Job Transfer Sets</t>
+  </si>
+  <si>
+    <t>10545684</t>
+  </si>
+  <si>
+    <t>10574315</t>
   </si>
   <si>
     <t>Additional Activities (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
   <si>
-    <t>Operations (Secondary) - WFM Secondary Job Transfer Sets</t>
+    <t>10580393</t>
+  </si>
+  <si>
+    <t>10596680</t>
+  </si>
+  <si>
+    <t>10622999</t>
+  </si>
+  <si>
+    <t>Returns (Secondary) - WFM Secondary Job Transfer Sets</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -88,11 +148,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,20 +187,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -403,15 +515,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" customWidth="1"/>
-    <col min="4" max="4" width="57.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="28.5546875" customWidth="1"/>
+    <col min="4" max="4" width="57.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -431,89 +543,322 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>10648828</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
+      <c r="E10" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="4"/>
+    </row>
+    <row r="15" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="4"/>
+    </row>
+    <row r="18" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="4"/>
+    </row>
+    <row r="22" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="4"/>
+    </row>
+    <row r="23" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="4"/>
+    </row>
+    <row r="24" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="4"/>
+    </row>
+    <row r="25" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="4"/>
+    </row>
+    <row r="26" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="4"/>
+    </row>
+    <row r="27" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="4"/>
+    </row>
+    <row r="28" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="4"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="4"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Failed"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Passed"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>